--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
   </si>
   <si>
     <t>В3914РТ</t>
@@ -119,8 +113,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -206,11 +201,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -218,9 +214,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -574,20 +570,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
         <v>1199</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>24.096</v>
@@ -605,7 +601,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -615,20 +611,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2">
+        <v>46146</v>
       </c>
       <c r="B3">
         <v>1199</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>32.901</v>
@@ -646,7 +642,7 @@
         <v>50.01</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -656,20 +652,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4" s="2">
+        <v>46153</v>
       </c>
       <c r="B4">
         <v>1158</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
       </c>
       <c r="F4">
         <v>9.753</v>
@@ -687,7 +683,7 @@
         <v>15.02</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -697,20 +693,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>14</v>
+      <c r="A5" s="2">
+        <v>46153</v>
       </c>
       <c r="B5">
         <v>1158</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
       </c>
       <c r="F5">
         <v>30.12</v>
@@ -728,7 +724,7 @@
         <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,115 +733,110 @@
         <v>94316</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="F6">
+    <row r="8" spans="1:13">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6">
+        <v>54.216</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.8201000000000001</v>
+      </c>
+      <c r="E10" s="6">
+        <v>44.46</v>
+      </c>
+      <c r="F10" s="6">
+        <v>45</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="6">
+        <v>42.654</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.4946</v>
+      </c>
+      <c r="E11" s="6">
+        <v>63.75</v>
+      </c>
+      <c r="F11" s="6">
+        <v>65.03</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="8">
         <v>96.87</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="5">
-        <v>54.216</v>
-      </c>
-      <c r="C11" s="5">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.8201000000000001</v>
-      </c>
-      <c r="E11" s="5">
-        <v>44.46</v>
-      </c>
-      <c r="F11" s="5">
-        <v>45</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="5">
-        <v>42.654</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.4946</v>
-      </c>
-      <c r="E12" s="5">
-        <v>63.75</v>
-      </c>
-      <c r="F12" s="5">
-        <v>65.03</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="7">
-        <v>96.87</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="C12" s="8">
         <v>4</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
         <v>108.21</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F12" s="8">
         <v>110.03</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G12" s="8">
         <v>1.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -170,7 +170,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,12 +180,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -236,17 +230,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,22 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна</t>
   </si>
   <si>
     <t>В3914РТ</t>
@@ -83,39 +71,6 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:51:00</t>
-  </si>
-  <si>
-    <t>18:28:00</t>
-  </si>
-  <si>
-    <t>14:18:00</t>
-  </si>
-  <si>
-    <t>14:19:00</t>
-  </si>
-  <si>
-    <t>12:37:00</t>
-  </si>
-  <si>
-    <t>3232078031 3232078031</t>
-  </si>
-  <si>
-    <t>3232114119 3232114119</t>
-  </si>
-  <si>
-    <t>3232436855 3232436855</t>
-  </si>
-  <si>
-    <t>3232436864 3232436864</t>
-  </si>
-  <si>
-    <t>3232548213 3232548213</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -535,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -544,17 +499,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,239 +540,185 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>31.19</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="H2">
+        <v>23.08</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="J2">
+        <v>23.39</v>
+      </c>
+      <c r="K2">
+        <v>180188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>31.65</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H3">
+        <v>48.74</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J3">
+        <v>49.69</v>
+      </c>
+      <c r="K3">
+        <v>180188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H4">
+        <v>14.71</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J4">
+        <v>14.99</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>34.72</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H5">
+        <v>24.65</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J5">
+        <v>25</v>
+      </c>
+      <c r="K5">
+        <v>180463</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>11.16</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H6">
+        <v>17.07</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J6">
+        <v>17.41</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>31.65</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2">
-        <v>0.78</v>
-      </c>
-      <c r="I2" s="1">
-        <v>24.69</v>
-      </c>
-      <c r="J2">
-        <v>0.79</v>
-      </c>
-      <c r="K2" s="1">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2">
-        <v>179756</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>10.65</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>1.52</v>
-      </c>
-      <c r="I3" s="1">
-        <v>16.19</v>
-      </c>
-      <c r="J3">
-        <v>1.55</v>
-      </c>
-      <c r="K3" s="1">
-        <v>16.51</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>11.72</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>1.54</v>
-      </c>
-      <c r="I4" s="1">
-        <v>18.05</v>
-      </c>
-      <c r="J4">
-        <v>1.57</v>
-      </c>
-      <c r="K4" s="1">
-        <v>18.4</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>32.05</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
-        <v>0.77</v>
-      </c>
-      <c r="I5" s="1">
-        <v>24.68</v>
-      </c>
-      <c r="J5">
-        <v>0.78</v>
-      </c>
-      <c r="K5" s="1">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5">
-        <v>179194</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>9.56</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>1.54</v>
-      </c>
-      <c r="I6" s="1">
-        <v>14.72</v>
-      </c>
-      <c r="J6">
-        <v>1.57</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15.01</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -828,82 +726,82 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B11" s="7">
-        <v>63.7</v>
+        <v>65.91</v>
       </c>
       <c r="C11" s="7">
         <v>2</v>
       </c>
       <c r="D11" s="8">
-        <v>0.775</v>
+        <v>0.7242</v>
       </c>
       <c r="E11" s="7">
-        <v>49.37</v>
+        <v>47.73</v>
       </c>
       <c r="F11" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>48.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B12" s="7">
-        <v>31.93</v>
+        <v>52.36</v>
       </c>
       <c r="C12" s="7">
         <v>3</v>
       </c>
       <c r="D12" s="8">
-        <v>1.5334</v>
+        <v>1.5378</v>
       </c>
       <c r="E12" s="7">
-        <v>48.96</v>
+        <v>80.52</v>
       </c>
       <c r="F12" s="7">
-        <v>49.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>82.09</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B13" s="10">
-        <v>95.63</v>
+        <v>118.27</v>
       </c>
       <c r="C13" s="10">
         <v>5</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>98.33</v>
+        <v>128.25</v>
       </c>
       <c r="F13" s="10">
-        <v>99.92</v>
+        <v>130.48</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -46,13 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>В3914РТ</t>
@@ -71,6 +77,18 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>11:44</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -490,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -503,10 +521,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -540,22 +560,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46175</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>31.19</v>
@@ -572,25 +598,31 @@
       <c r="J2">
         <v>23.39</v>
       </c>
-      <c r="K2">
-        <v>180188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
+        <v>89505</v>
+      </c>
+      <c r="M2">
+        <v>137738</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46175</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>31.65</v>
@@ -607,25 +639,31 @@
       <c r="J3">
         <v>49.69</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
         <v>180188</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>137738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46178</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>9.550000000000001</v>
@@ -642,25 +680,31 @@
       <c r="J4">
         <v>14.99</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>138891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46182</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>34.72</v>
@@ -677,25 +721,31 @@
       <c r="J5">
         <v>25</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5">
         <v>180463</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>273799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46184</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>11.16</v>
@@ -712,13 +762,19 @@
       <c r="J6">
         <v>17.41</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M6">
+        <v>140921</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -726,18 +782,18 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>7</v>
@@ -746,9 +802,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="7">
         <v>65.91</v>
@@ -766,9 +822,9 @@
         <v>48.39</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="7">
         <v>52.36</v>
@@ -786,9 +842,9 @@
         <v>82.09</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B13" s="10">
         <v>118.27</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -49,46 +49,40 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>ТубаКам1</t>
   </si>
   <si>
     <t>В3914РТ</t>
   </si>
   <si>
-    <t>ТубаКам1</t>
+    <t>78970155027720824</t>
   </si>
   <si>
     <t>78970155027720816</t>
   </si>
   <si>
-    <t>78970155027720824</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>13:17</t>
-  </si>
-  <si>
-    <t>13:28</t>
-  </si>
-  <si>
-    <t>11:44</t>
+    <t>2026-06-17 12:04:04</t>
+  </si>
+  <si>
+    <t>2026-06-17 12:06:29</t>
+  </si>
+  <si>
+    <t>2026-06-22 12:33:25</t>
+  </si>
+  <si>
+    <t>2026-06-24 14:00:33</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -508,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,12 +515,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,309 +552,238 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>15.2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>15.5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>29.85</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H3">
+        <v>19.7</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>11.85</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H4">
+        <v>17.54</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J4">
+        <v>17.89</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>30.3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H5">
+        <v>19.7</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="7">
+        <v>60.15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.655</v>
+      </c>
+      <c r="E10" s="7">
+        <v>39.4</v>
+      </c>
+      <c r="F10" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2">
-        <v>31.19</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="H2">
-        <v>23.08</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="J2">
-        <v>23.39</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>89505</v>
-      </c>
-      <c r="M2">
-        <v>137738</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>31.65</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H3">
-        <v>48.74</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J3">
-        <v>49.69</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>180188</v>
-      </c>
-      <c r="M3">
-        <v>137738</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46178</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H4">
-        <v>14.71</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J4">
-        <v>14.99</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>138891</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>34.72</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H5">
-        <v>24.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J5">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5">
-        <v>180463</v>
-      </c>
-      <c r="M5">
-        <v>273799</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>11.16</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H6">
-        <v>17.07</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J6">
-        <v>17.41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>140921</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="B11" s="7">
-        <v>65.91</v>
+        <v>21.85</v>
       </c>
       <c r="C11" s="7">
         <v>2</v>
       </c>
       <c r="D11" s="8">
-        <v>0.7242</v>
+        <v>1.4984</v>
       </c>
       <c r="E11" s="7">
-        <v>47.73</v>
+        <v>32.74</v>
       </c>
       <c r="F11" s="7">
-        <v>48.39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="7">
-        <v>52.36</v>
-      </c>
-      <c r="C12" s="7">
-        <v>3</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1.5378</v>
-      </c>
-      <c r="E12" s="7">
-        <v>80.52</v>
-      </c>
-      <c r="F12" s="7">
-        <v>82.09</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="10">
-        <v>118.27</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="10">
-        <v>128.25</v>
-      </c>
-      <c r="F13" s="10">
-        <v>130.48</v>
+        <v>33.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="10">
+        <v>82</v>
+      </c>
+      <c r="C12" s="10">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>72.14</v>
+      </c>
+      <c r="F12" s="10">
+        <v>73.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,16 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>ТубаКам1</t>
@@ -73,16 +82,37 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-17 12:04:04</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:06:29</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:33:25</t>
-  </si>
-  <si>
-    <t>2026-06-24 14:00:33</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:04:00</t>
+  </si>
+  <si>
+    <t>12:07:00</t>
+  </si>
+  <si>
+    <t>12:33:00</t>
+  </si>
+  <si>
+    <t>13:59:00</t>
+  </si>
+  <si>
+    <t>09:11:00</t>
+  </si>
+  <si>
+    <t>3233473073 3233473073</t>
+  </si>
+  <si>
+    <t>3233473074 3233473074</t>
+  </si>
+  <si>
+    <t>3233710381 3233710381</t>
+  </si>
+  <si>
+    <t>3233809335 3233809335</t>
+  </si>
+  <si>
+    <t>3234095857 3234095857</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -502,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,14 +541,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -552,238 +585,327 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46190</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>1.52</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>15.2</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.55</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>15.5</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46190</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>29.85</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>0.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>19.7</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.67</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>180722</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>11.85</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
         <v>1.48</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>17.54</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.51</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>17.89</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>30.3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
         <v>0.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>19.7</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.66</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>20</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>181002</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>10.67</v>
+      </c>
+      <c r="G6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="H6">
+        <v>1.47</v>
+      </c>
+      <c r="I6" s="1">
+        <v>15.68</v>
+      </c>
+      <c r="J6">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>16</v>
+      </c>
+      <c r="L6" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="7">
         <v>60.15</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.655</v>
-      </c>
-      <c r="E10" s="7">
-        <v>39.4</v>
-      </c>
-      <c r="F10" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="7">
-        <v>21.85</v>
       </c>
       <c r="C11" s="7">
         <v>2</v>
       </c>
       <c r="D11" s="8">
-        <v>1.4984</v>
+        <v>0.655</v>
       </c>
       <c r="E11" s="7">
-        <v>32.74</v>
+        <v>39.4</v>
       </c>
       <c r="F11" s="7">
-        <v>33.39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="10">
-        <v>82</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>72.14</v>
-      </c>
-      <c r="F12" s="10">
-        <v>73.39</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="7">
+        <v>32.52</v>
+      </c>
+      <c r="C12" s="7">
+        <v>3</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1.4889</v>
+      </c>
+      <c r="E12" s="7">
+        <v>48.42</v>
+      </c>
+      <c r="F12" s="7">
+        <v>49.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="10">
+        <v>92.67</v>
+      </c>
+      <c r="C13" s="10">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="F13" s="10">
+        <v>89.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,13 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>ТубаКам1</t>
@@ -82,37 +82,19 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:04:00</t>
-  </si>
-  <si>
-    <t>12:07:00</t>
-  </si>
-  <si>
-    <t>12:33:00</t>
-  </si>
-  <si>
-    <t>13:59:00</t>
-  </si>
-  <si>
-    <t>09:11:00</t>
-  </si>
-  <si>
-    <t>3233473073 3233473073</t>
-  </si>
-  <si>
-    <t>3233473074 3233473074</t>
-  </si>
-  <si>
-    <t>3233710381 3233710381</t>
-  </si>
-  <si>
-    <t>3233809335 3233809335</t>
-  </si>
-  <si>
-    <t>3234095857 3234095857</t>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>09:11</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -532,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -541,17 +523,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,16 +572,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46190</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -614,32 +592,29 @@
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>15.2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>15.5</v>
+      </c>
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15.5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>143005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46190</v>
       </c>
@@ -658,37 +633,34 @@
       <c r="F3">
         <v>29.85</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
+      <c r="G3" s="1">
+        <v>0.66</v>
       </c>
       <c r="H3">
-        <v>0.66</v>
+        <v>19.7</v>
       </c>
       <c r="I3" s="1">
-        <v>19.7</v>
+        <v>0.67</v>
       </c>
       <c r="J3">
-        <v>0.67</v>
-      </c>
-      <c r="K3" s="1">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
-        <v>24</v>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>180722</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>143006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46195</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -702,32 +674,29 @@
       <c r="F4">
         <v>11.85</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
+      <c r="G4" s="1">
+        <v>1.48</v>
       </c>
       <c r="H4">
-        <v>1.48</v>
+        <v>17.54</v>
       </c>
       <c r="I4" s="1">
-        <v>17.54</v>
+        <v>1.51</v>
       </c>
       <c r="J4">
-        <v>1.51</v>
-      </c>
-      <c r="K4" s="1">
         <v>17.89</v>
       </c>
-      <c r="L4" t="s">
-        <v>25</v>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>144530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46197</v>
       </c>
@@ -746,32 +715,29 @@
       <c r="F5">
         <v>30.3</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
+      <c r="G5" s="1">
+        <v>0.65</v>
       </c>
       <c r="H5">
-        <v>0.65</v>
+        <v>19.7</v>
       </c>
       <c r="I5" s="1">
-        <v>19.7</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>0.66</v>
-      </c>
-      <c r="K5" s="1">
         <v>20</v>
       </c>
-      <c r="L5" t="s">
-        <v>26</v>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5">
+        <v>181002</v>
       </c>
       <c r="M5">
-        <v>181002</v>
-      </c>
-      <c r="N5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>2731</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46203</v>
       </c>
@@ -790,34 +756,31 @@
       <c r="F6">
         <v>10.67</v>
       </c>
-      <c r="G6" t="s">
-        <v>22</v>
+      <c r="G6" s="1">
+        <v>1.47</v>
       </c>
       <c r="H6">
-        <v>1.47</v>
+        <v>15.68</v>
       </c>
       <c r="I6" s="1">
-        <v>15.68</v>
+        <v>1.5</v>
       </c>
       <c r="J6">
-        <v>1.5</v>
-      </c>
-      <c r="K6" s="1">
         <v>16</v>
       </c>
-      <c r="L6" t="s">
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>121428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -825,27 +788,27 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
@@ -865,7 +828,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
@@ -885,9 +848,9 @@
         <v>49.39</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B13" s="10">
         <v>92.67</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,46 +55,58 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>В3914РТ</t>
   </si>
   <si>
     <t>ТубаКам1</t>
   </si>
   <si>
-    <t>В3914РТ</t>
+    <t>78970155027720816</t>
   </si>
   <si>
     <t>78970155027720824</t>
   </si>
   <si>
-    <t>78970155027720816</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>2026-07-03 12:35:53</t>
-  </si>
-  <si>
-    <t>2026-07-03 12:37:15</t>
-  </si>
-  <si>
-    <t>2026-07-03 12:37:16</t>
-  </si>
-  <si>
-    <t>2026-07-09 13:00:44</t>
-  </si>
-  <si>
-    <t>2026-07-10 14:00:58</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:52:51</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:22:00</t>
+  </si>
+  <si>
+    <t>12:51:00</t>
+  </si>
+  <si>
+    <t>10:39:00</t>
+  </si>
+  <si>
+    <t>12:41:00</t>
+  </si>
+  <si>
+    <t>3234937033 3234937033</t>
+  </si>
+  <si>
+    <t>3235220172 3235220172</t>
+  </si>
+  <si>
+    <t>3235492864 3235492864</t>
+  </si>
+  <si>
+    <t>3235510032 3235510032</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -511,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,15 +535,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -565,326 +582,260 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46206</v>
+        <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>19.87</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>1.48</v>
+      </c>
+      <c r="I2" s="1">
+        <v>29.41</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>181691</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>19.48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
+        <v>1.51</v>
+      </c>
+      <c r="I3" s="1">
+        <v>29.41</v>
+      </c>
+      <c r="J3">
+        <v>1.54</v>
+      </c>
+      <c r="K3" s="1">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>181811</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>10.67</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H2">
-        <v>15.68</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="L2">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>11.55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>1.53</v>
+      </c>
+      <c r="I4" s="1">
+        <v>17.67</v>
+      </c>
+      <c r="J4">
+        <v>1.56</v>
+      </c>
+      <c r="K4" s="1">
+        <v>18.02</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46206</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>33.33</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H3">
-        <v>49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J3">
-        <v>50</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>181281</v>
+      <c r="F5">
+        <v>10.97</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>1.52</v>
+      </c>
+      <c r="I5" s="1">
+        <v>16.67</v>
+      </c>
+      <c r="J5">
+        <v>1.55</v>
+      </c>
+      <c r="K5" s="1">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>181974</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46206</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>31.25</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="H4">
-        <v>19.69</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="J4">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>181281</v>
-      </c>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46212</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>3.13</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H5">
-        <v>1.94</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J5">
-        <v>1.97</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5">
-        <v>181480</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3">
-        <v>46213</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>10.74</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H6">
-        <v>15.68</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="7">
+        <v>61.87</v>
+      </c>
+      <c r="C10" s="7">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.5057</v>
+      </c>
+      <c r="E10" s="7">
+        <v>93.16</v>
+      </c>
+      <c r="F10" s="7">
+        <v>95.02</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3">
-        <v>46218</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>11.4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H7">
-        <v>16.64</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J7">
-        <v>16.99</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7">
-        <v>66.14</v>
-      </c>
-      <c r="C12" s="7">
+    <row r="11" spans="1:14">
+      <c r="A11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="10">
+        <v>61.87</v>
+      </c>
+      <c r="C11" s="10">
         <v>4</v>
       </c>
-      <c r="D12" s="8">
-        <v>1.4666</v>
-      </c>
-      <c r="E12" s="7">
-        <v>97</v>
-      </c>
-      <c r="F12" s="7">
-        <v>98.98999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="7">
-        <v>34.38</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.6291</v>
-      </c>
-      <c r="E13" s="7">
-        <v>21.63</v>
-      </c>
-      <c r="F13" s="7">
-        <v>21.97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="10">
-        <v>100.52</v>
-      </c>
-      <c r="C14" s="10">
-        <v>6</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10">
-        <v>118.63</v>
-      </c>
-      <c r="F14" s="10">
-        <v>120.96</v>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>93.16</v>
+      </c>
+      <c r="F11" s="10">
+        <v>95.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -134,7 +134,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -806,7 +806,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>1.5057</v>
+        <v>1.505738</v>
       </c>
       <c r="E10" s="7">
         <v>93.16</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -526,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -539,13 +542,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,186 +591,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>19.87</v>
+        <v>19.868</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2">
+        <v>1.369</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.48</v>
       </c>
-      <c r="I2" s="1">
-        <v>29.41</v>
-      </c>
       <c r="J2">
+        <v>29.40464</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>30.00068</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
         <v>181691</v>
       </c>
-      <c r="N2" t="s">
-        <v>27</v>
+      <c r="O2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46226</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>19.48</v>
+        <v>19.481</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3">
+        <v>1.401</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.51</v>
       </c>
-      <c r="I3" s="1">
-        <v>29.41</v>
-      </c>
       <c r="J3">
+        <v>29.41631</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.54</v>
       </c>
-      <c r="K3" s="1">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>30.00074</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
         <v>181811</v>
       </c>
-      <c r="N3" t="s">
-        <v>28</v>
+      <c r="O3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>11.55</v>
+        <v>11.551</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4">
+        <v>1.441</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.53</v>
       </c>
-      <c r="I4" s="1">
-        <v>17.67</v>
-      </c>
       <c r="J4">
+        <v>17.67303</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.56</v>
       </c>
-      <c r="K4" s="1">
-        <v>18.02</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>18.01956</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>29</v>
+      <c r="O4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46232</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>10.97</v>
+        <v>10.968</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5">
+        <v>1.449</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.52</v>
       </c>
-      <c r="I5" s="1">
-        <v>16.67</v>
-      </c>
       <c r="J5">
+        <v>16.67136</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.55</v>
       </c>
-      <c r="K5" s="1">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>17.0004</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
         <v>181974</v>
       </c>
-      <c r="N5" t="s">
-        <v>30</v>
+      <c r="O5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -775,59 +793,59 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7">
-        <v>61.87</v>
+        <v>61.868</v>
       </c>
       <c r="C10" s="7">
         <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>1.505738</v>
+        <v>1.505873</v>
       </c>
       <c r="E10" s="7">
-        <v>93.16</v>
+        <v>93.17</v>
       </c>
       <c r="F10" s="7">
         <v>95.02</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="10">
-        <v>61.87</v>
+        <v>61.868</v>
       </c>
       <c r="C11" s="10">
         <v>4</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>93.16</v>
+        <v>93.17</v>
       </c>
       <c r="F11" s="10">
         <v>95.02</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -135,9 +132,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -231,10 +228,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -542,13 +539,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,201 +588,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46220</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>19.868</v>
       </c>
       <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>1.48</v>
+      </c>
+      <c r="I2" s="1">
+        <v>29.405</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30.001</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="J2">
-        <v>29.40464</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>30.00068</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>181691</v>
       </c>
-      <c r="O2" t="s">
-        <v>28</v>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46226</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>19.481</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I3" s="1">
-        <v>1.51</v>
+        <v>29.416</v>
       </c>
       <c r="J3">
-        <v>29.41631</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>30.00074</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
+        <v>30.001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>181811</v>
       </c>
-      <c r="O3" t="s">
-        <v>29</v>
+      <c r="N3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4">
         <v>11.551</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I4" s="1">
-        <v>1.53</v>
+        <v>17.673</v>
       </c>
       <c r="J4">
-        <v>17.67303</v>
+        <v>1.56</v>
       </c>
       <c r="K4" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L4" s="1">
-        <v>18.01956</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4">
+        <v>18.02</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>30</v>
+      <c r="N4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46232</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>10.968</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I5" s="1">
-        <v>1.52</v>
+        <v>16.671</v>
       </c>
       <c r="J5">
-        <v>16.67136</v>
+        <v>1.55</v>
       </c>
       <c r="K5" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L5" s="1">
-        <v>17.0004</v>
-      </c>
-      <c r="M5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
         <v>181974</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -793,49 +775,49 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7">
         <v>61.868</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>1.505873</v>
-      </c>
-      <c r="E10" s="7">
-        <v>93.17</v>
-      </c>
-      <c r="F10" s="7">
-        <v>95.02</v>
+        <v>1.506</v>
+      </c>
+      <c r="E10" s="8">
+        <v>93.16500000000001</v>
+      </c>
+      <c r="F10" s="8">
+        <v>95.02200000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="10">
         <v>61.868</v>
@@ -845,10 +827,10 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>93.17</v>
+        <v>93.16500000000001</v>
       </c>
       <c r="F11" s="10">
-        <v>95.02</v>
+        <v>95.02200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,55 +55,34 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>ТубаКам1</t>
   </si>
   <si>
     <t>В3914РТ</t>
   </si>
   <si>
-    <t>ТубаКам1</t>
+    <t>78970155027720824</t>
   </si>
   <si>
     <t>78970155027720816</t>
   </si>
   <si>
-    <t>78970155027720824</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>13:22:00</t>
-  </si>
-  <si>
-    <t>12:51:00</t>
-  </si>
-  <si>
-    <t>10:39:00</t>
-  </si>
-  <si>
-    <t>12:41:00</t>
-  </si>
-  <si>
-    <t>3234937033 3234937033</t>
-  </si>
-  <si>
-    <t>3235220172 3235220172</t>
-  </si>
-  <si>
-    <t>3235492864 3235492864</t>
-  </si>
-  <si>
-    <t>3235510032 3235510032</t>
+    <t>22:12</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>13:14</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -132,9 +108,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -228,10 +204,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -535,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,257 +560,283 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46220</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>10.323</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>15.691</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>16.001</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>55904</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>32.258</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H3">
+        <v>49.032</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J3">
+        <v>50</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="L3">
+        <v>182106</v>
+      </c>
+      <c r="M3">
+        <v>55905</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>32.258</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H4">
+        <v>49.032</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J4">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>182322</v>
+      </c>
+      <c r="M4">
+        <v>161584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
+        <v>10.323</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H5">
+        <v>15.691</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J5">
+        <v>16.001</v>
+      </c>
+      <c r="K5" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>19.868</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>161585</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>10.323</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H6">
+        <v>15.691</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J6">
+        <v>16.001</v>
+      </c>
+      <c r="K6" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1.48</v>
-      </c>
-      <c r="I2" s="1">
-        <v>29.405</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>30.001</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>162944</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M2">
-        <v>181691</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46226</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>19.481</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3">
-        <v>1.51</v>
-      </c>
-      <c r="I3" s="1">
-        <v>29.416</v>
-      </c>
-      <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
-        <v>30.001</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>181811</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="E10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7">
+        <v>95.485</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E11" s="7">
+        <v>145.14</v>
+      </c>
+      <c r="F11" s="7">
+        <v>148.003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>11.551</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4">
-        <v>1.53</v>
-      </c>
-      <c r="I4" s="1">
-        <v>17.673</v>
-      </c>
-      <c r="J4">
-        <v>1.56</v>
-      </c>
-      <c r="K4" s="1">
-        <v>18.02</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46232</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>10.968</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5">
-        <v>1.52</v>
-      </c>
-      <c r="I5" s="1">
-        <v>16.671</v>
-      </c>
-      <c r="J5">
-        <v>1.55</v>
-      </c>
-      <c r="K5" s="1">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
-        <v>181974</v>
-      </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7">
-        <v>61.868</v>
-      </c>
-      <c r="C10" s="8">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.506</v>
-      </c>
-      <c r="E10" s="8">
-        <v>93.16500000000001</v>
-      </c>
-      <c r="F10" s="8">
-        <v>95.02200000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="10">
-        <v>61.868</v>
-      </c>
-      <c r="C11" s="10">
-        <v>4</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>93.16500000000001</v>
-      </c>
-      <c r="F11" s="10">
-        <v>95.02200000000001</v>
+      <c r="B12" s="10">
+        <v>95.485</v>
+      </c>
+      <c r="C12" s="10">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>145.14</v>
+      </c>
+      <c r="F12" s="10">
+        <v>148.003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,34 +58,49 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>В3914РТ</t>
   </si>
   <si>
     <t>ТубаКам1</t>
   </si>
   <si>
-    <t>В3914РТ</t>
+    <t>78970155027720816</t>
   </si>
   <si>
     <t>78970155027720824</t>
   </si>
   <si>
-    <t>78970155027720816</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>22:12</t>
-  </si>
-  <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>13:14</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:38:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>10:44:00</t>
+  </si>
+  <si>
+    <t>3236592676 3236592676</t>
+  </si>
+  <si>
+    <t>3236592677 3236592677</t>
+  </si>
+  <si>
+    <t>3236956215 3236956215</t>
+  </si>
+  <si>
+    <t>3237049758 3237049758</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -107,10 +125,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -190,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -204,10 +223,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,16 +532,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,283 +582,257 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46235</v>
+        <v>46253</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>33.33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>47.629</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="1">
+        <v>51.995</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
+        <v>182589</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>10.323</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>15.691</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J2">
-        <v>16.001</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>11.76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I3" s="1">
+        <v>16.805</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K3" s="1">
+        <v>18.346</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>55904</v>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46235</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>32.258</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>49.032</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>50</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
-        <v>182106</v>
-      </c>
-      <c r="M3">
-        <v>55905</v>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>10.76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I4" s="1">
+        <v>15.699</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K4" s="1">
+        <v>17.001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46244</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>32.258</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H4">
-        <v>49.032</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J4">
-        <v>50</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="L4">
-        <v>182322</v>
-      </c>
-      <c r="M4">
-        <v>161584</v>
+      <c r="F5">
+        <v>10.69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.459</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15.597</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="K5" s="1">
+        <v>16.997</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46244</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>10.323</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H5">
-        <v>15.691</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J5">
-        <v>16.001</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>161585</v>
-      </c>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>10.323</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H6">
-        <v>15.691</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J6">
-        <v>16.001</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>162944</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.43868</v>
+      </c>
+      <c r="E10" s="7">
+        <v>95.73</v>
+      </c>
+      <c r="F10" s="7">
+        <v>104.34</v>
+      </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="7">
-        <v>95.485</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E11" s="7">
-        <v>145.14</v>
-      </c>
-      <c r="F11" s="7">
-        <v>148.003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="10">
-        <v>95.485</v>
-      </c>
-      <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>145.14</v>
-      </c>
-      <c r="F12" s="10">
-        <v>148.003</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="11">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="C11" s="12">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11">
+        <v>95.73</v>
+      </c>
+      <c r="F11" s="11">
+        <v>104.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -609,10 +609,10 @@
         <v>21</v>
       </c>
       <c r="H2" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I2" s="1">
-        <v>47.629</v>
+        <v>50.995</v>
       </c>
       <c r="J2" s="1">
         <v>1.56</v>
@@ -653,10 +653,10 @@
         <v>21</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>16.805</v>
+        <v>17.993</v>
       </c>
       <c r="J3" s="1">
         <v>1.56</v>
@@ -697,10 +697,10 @@
         <v>21</v>
       </c>
       <c r="H4" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I4" s="1">
-        <v>15.699</v>
+        <v>16.678</v>
       </c>
       <c r="J4" s="1">
         <v>1.58</v>
@@ -741,10 +741,10 @@
         <v>21</v>
       </c>
       <c r="H5" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I5" s="1">
-        <v>15.597</v>
+        <v>16.676</v>
       </c>
       <c r="J5" s="1">
         <v>1.59</v>
@@ -803,10 +803,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="9">
-        <v>1.43868</v>
+        <v>1.53805</v>
       </c>
       <c r="E10" s="7">
-        <v>95.73</v>
+        <v>102.34</v>
       </c>
       <c r="F10" s="7">
         <v>104.34</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="11">
-        <v>95.73</v>
+        <v>102.34</v>
       </c>
       <c r="F11" s="11">
         <v>104.34</v>
